--- a/data/trans_orig/IP11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -718,112 +718,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -831,112 +831,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>86753</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>82466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>88935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>84006</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>79955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>86051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>170758</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>164807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>174192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -944,342 +944,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90867</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>90867</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>90867</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>86753</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>82448</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>89351</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84006</t>
+          <t>86845</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80103</t>
+          <t>86845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86046</t>
+          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>170758</t>
+          <t>177712</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165666</t>
+          <t>177712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>174299</t>
+          <t>177712</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90867</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90867</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90867</t>
+          <t>28973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>36922</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>28141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>47135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>177712</t>
+          <t>57968</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177712</t>
+          <t>47516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177712</t>
+          <t>70129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>596</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395041</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>401457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>663</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>440069</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>448850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>835110</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>822949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>845562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -1287,225 +1287,229 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>628</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>416087</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>416087</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>416087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>719</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36922</t>
+          <t>476991</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>476991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47088</t>
+          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>57968</t>
+          <t>893078</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47588</t>
+          <t>893078</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71677</t>
+          <t>893078</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>395041</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>386840</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>401272</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>440069</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>429903</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>448567</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>835110</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>821401</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>845490</t>
+          <t>24525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1513,234 +1517,234 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>239</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>416087</t>
+          <t>163922</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416087</t>
+          <t>157856</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>416087</t>
+          <t>168218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>226</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>476991</t>
+          <t>151374</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>476991</t>
+          <t>146227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>476991</t>
+          <t>154813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>465</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>893078</t>
+          <t>315297</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>893078</t>
+          <t>307680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>893078</t>
+          <t>321143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>254</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174066</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174066</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>158138</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158138</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332205</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332205</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332205</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1748,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>35304</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>45694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36863</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>81829</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>67454</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>96435</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>5,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3466</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11642</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>16908</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>10802</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>23798</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1861,107 +1865,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>965</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>163922</t>
+          <t>645717</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157872</t>
+          <t>635327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168475</t>
+          <t>654834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>675449</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>663151</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>685111</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1321166</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1306560</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1335541</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>94,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>151374</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>146496</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>154672</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>315297</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>308407</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>321403</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1974,22 +1978,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>174066</t>
+          <t>681021</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174066</t>
+          <t>681021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174066</t>
+          <t>681021</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2009,22 +2013,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>158138</t>
+          <t>721974</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>158138</t>
+          <t>721974</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>158138</t>
+          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2044,22 +2048,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332205</t>
+          <t>1402995</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332205</t>
+          <t>1402995</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332205</t>
+          <t>1402995</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2079,463 +2083,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>No recogida en edición</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>35304</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27177</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>45823</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36516</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>57759</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>81829</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>67138</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>96180</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>645717</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>635198</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653844</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>93,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>675449</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>664215</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>685458</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1321166</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1306815</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>1335857</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>681021</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>681021</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>681021</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1402995</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1402995</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1402995</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -2544,13 +2092,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2562,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2773,112 +2321,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -2886,112 +2434,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>88316</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>84677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>90964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>73608</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>66874</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>78501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>161924</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>153740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>167454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -2999,342 +2547,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>134</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88316</t>
+          <t>92369</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84150</t>
+          <t>92369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90954</t>
+          <t>92369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73608</t>
+          <t>86192</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>86192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78751</t>
+          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>161924</t>
+          <t>178561</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154692</t>
+          <t>178561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167994</t>
+          <t>178561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>37951</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>29146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>49528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>35030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>56439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>178561</t>
+          <t>82845</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178561</t>
+          <t>69164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178561</t>
+          <t>98062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>413848</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>402271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>422653</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447861</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>436316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>457725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>861709</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>846492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>875390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -3342,225 +2890,229 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>654</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37951</t>
+          <t>451799</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>451799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48298</t>
+          <t>451799</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>706</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44894</t>
+          <t>492755</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>492755</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56729</t>
+          <t>492755</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>82845</t>
+          <t>944554</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69866</t>
+          <t>944554</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99817</t>
+          <t>944554</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>413848</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>403501</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>423248</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>447861</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>436026</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>458484</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>861709</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>844737</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>874688</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3568,234 +3120,234 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>451799</t>
+          <t>157104</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451799</t>
+          <t>151396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451799</t>
+          <t>161530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>220</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>492755</t>
+          <t>155582</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>492755</t>
+          <t>148582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>492755</t>
+          <t>161289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>442</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>944554</t>
+          <t>312686</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>944554</t>
+          <t>303563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>944554</t>
+          <t>319815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166812</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166812</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171481</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338293</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338293</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -3803,107 +3355,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>40579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>65077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>105</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>73377</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>60991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>86973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>125089</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>108165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33978</t>
+          <t>143608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -3916,107 +3468,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>949</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>157104</t>
+          <t>659268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150921</t>
+          <t>645903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161124</t>
+          <t>670401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>965</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>155582</t>
+          <t>677051</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148040</t>
+          <t>663455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160806</t>
+          <t>689437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>312686</t>
+          <t>1336319</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304315</t>
+          <t>1317800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319941</t>
+          <t>1353243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -4029,22 +3581,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>166812</t>
+          <t>710980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166812</t>
+          <t>710980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166812</t>
+          <t>710980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4064,22 +3616,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>171481</t>
+          <t>750428</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>171481</t>
+          <t>750428</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171481</t>
+          <t>750428</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4099,22 +3651,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>338293</t>
+          <t>1461408</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>338293</t>
+          <t>1461408</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>338293</t>
+          <t>1461408</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4134,463 +3686,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>No recogida en edición</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>51712</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>41383</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>63152</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>61571</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>87877</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>125089</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>107955</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>144451</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>659268</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>647828</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>669597</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>677051</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>662551</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>688857</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>88,29%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>91,8%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1914</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1336319</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1316957</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>1353453</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>91,44%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>710980</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>710980</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>710980</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>750428</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>750428</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>750428</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1461408</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1461408</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1461408</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -4599,13 +3695,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4617,7 +3713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4828,112 +3924,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -4941,112 +4037,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>56921</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>53554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>58767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>62214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>123007</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>118647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>125661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -5054,342 +4150,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56921</t>
+          <t>59378</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53403</t>
+          <t>59378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58753</t>
+          <t>59378</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66085</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62868</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67964</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>188</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>123007</t>
+          <t>127993</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118322</t>
+          <t>127993</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125618</t>
+          <t>127993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59378</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59378</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59378</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>23405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>40687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>69</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>127993</t>
+          <t>47890</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127993</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127993</t>
+          <t>59181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>688</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>455173</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>447958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>456683</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>447386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>464668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>911856</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>900565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>922411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -5397,225 +4493,229 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>713</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>471673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>471673</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>471673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>694</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31390</t>
+          <t>488073</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>488073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41191</t>
+          <t>488073</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47890</t>
+          <t>959746</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>959746</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60950</t>
+          <t>959746</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>455173</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>448445</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>460961</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>456683</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>446882</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>464615</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>911856</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>898796</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>920708</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5623,234 +4723,234 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>471673</t>
+          <t>166598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471673</t>
+          <t>162085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471673</t>
+          <t>169190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>260</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>488073</t>
+          <t>180011</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>488073</t>
+          <t>174509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>488073</t>
+          <t>183372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>509</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>959746</t>
+          <t>346608</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959746</t>
+          <t>340543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>959746</t>
+          <t>350974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>256</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186816</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>526</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>357826</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357826</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357826</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -5858,107 +4958,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>31776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>40724</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>52052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>64093</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>76910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5971,107 +5071,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>166598</t>
+          <t>678692</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162182</t>
+          <t>670285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169173</t>
+          <t>684837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>180011</t>
+          <t>702779</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175168</t>
+          <t>691451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183445</t>
+          <t>712126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>346608</t>
+          <t>1381471</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340823</t>
+          <t>1368654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351231</t>
+          <t>1392867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -6084,22 +5184,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>171010</t>
+          <t>702061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171010</t>
+          <t>702061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171010</t>
+          <t>702061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6119,22 +5219,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>186816</t>
+          <t>743503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>186816</t>
+          <t>743503</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>186816</t>
+          <t>743503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6154,22 +5254,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>357826</t>
+          <t>1445564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>357826</t>
+          <t>1445564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>357826</t>
+          <t>1445564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6189,463 +5289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>No recogida en edición</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>23369</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16956</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>32398</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>31315</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>52415</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>64093</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>52335</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>77356</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>678692</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>669663</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>685105</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>702779</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>691088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>712188</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1381471</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1368208</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>1393229</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>94,65%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>702061</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>702061</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>702061</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1445564</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1445564</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1445564</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -6654,13 +5298,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6672,7 +5316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6883,112 +5527,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6094</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -6996,112 +5640,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>53596</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>60654</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>149</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>114250</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>108929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>116048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -7109,22 +5753,22 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53596</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51002</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7134,32 +5778,32 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60654</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7169,282 +5813,282 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>152</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>114250</t>
+          <t>116682</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108747</t>
+          <t>116682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116226</t>
+          <t>116682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>22548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>624</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>448259</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>442241</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>453074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>636</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500793</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>949053</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>956672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -7452,225 +6096,229 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>641</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>459278</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>459278</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>459278</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>655</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>515539</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>515539</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>515539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>974818</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18672</t>
+          <t>974818</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35757</t>
+          <t>974818</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>448260</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>439865</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>452804</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>500793</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>492973</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>506441</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>949052</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>938869</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>956602</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7678,234 +6326,234 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>460094</t>
+          <t>144500</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460094</t>
+          <t>139451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>460094</t>
+          <t>147247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>229</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>515539</t>
+          <t>175412</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>515539</t>
+          <t>167558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515539</t>
+          <t>179444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>452</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>975633</t>
+          <t>319912</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>975633</t>
+          <t>312027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>975633</t>
+          <t>325354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>No recogida en edición</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>468</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332900</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332900</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332900</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -7913,107 +6561,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>24034</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>41185</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>52871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8026,107 +6674,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>914</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>144500</t>
+          <t>646356</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139605</t>
+          <t>638609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147249</t>
+          <t>652536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>175412</t>
+          <t>736858</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168556</t>
+          <t>725834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179271</t>
+          <t>744524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>319912</t>
+          <t>1383214</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311321</t>
+          <t>1371528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324993</t>
+          <t>1393698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -8139,22 +6787,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>940</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149551</t>
+          <t>663507</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149551</t>
+          <t>663507</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149551</t>
+          <t>663507</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8174,22 +6822,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>760892</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>760892</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>760892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8209,22 +6857,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>1424399</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>1424399</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>1424399</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8244,463 +6892,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>No recogida en edición</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11007</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24390</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24034</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16495</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34648</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>41185</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>30636</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>53122</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>646356</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>639052</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>652674</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>736858</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>726244</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744397</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1383215</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1370802</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>1393761</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>664323</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>664323</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>664323</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>760892</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>760892</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>760892</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1425215</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1425215</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1425215</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -8709,13 +6901,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP11-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7624</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8401</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8165</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6890</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84006</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79221</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86153</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>86753</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82466</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88935</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>82702</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>89458</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84006</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79955</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86051</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164807</t>
+          <t>165657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174192</t>
+          <t>174309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36922</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28954</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47674</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21046</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14630</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28973</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14784</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28756</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>36922</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>47135</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47516</t>
+          <t>45635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70129</t>
+          <t>69415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>440069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>429317</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>448037</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>596</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>395041</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>387114</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>401457</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>387331</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>401303</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>440069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>429856</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>448850</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,26%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>822949</t>
+          <t>823663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>845562</t>
+          <t>847443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11978</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10144</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5848</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16210</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16878</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11911</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>23684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>151374</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146160</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154814</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>163922</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>157856</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168218</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>157188</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>168115</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>151374</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>146227</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>154813</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307680</t>
+          <t>308521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321143</t>
+          <t>321073</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36602</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>58346</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26187</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>45694</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>26221</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>45310</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36863</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58823</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>68004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96435</t>
+          <t>95812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>675449</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>663628</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>685372</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>645717</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>635327</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>654834</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>635711</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>654800</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>96,15%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>675449</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>663151</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>685111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1980</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1306560</t>
+          <t>1307183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1335541</t>
+          <t>1334991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12584</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7913</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19329</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4053</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7692</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8608</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12584</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7691</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19318</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,6%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73608</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66863</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78279</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88316</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84677</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>90964</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>83761</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>90541</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73608</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>66874</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78501</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,4%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153740</t>
+          <t>154128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167454</t>
+          <t>167891</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>44894</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35030</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56519</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>37951</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29146</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>49528</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>28635</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>47623</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>44894</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>35030</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>56439</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69164</t>
+          <t>69583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98062</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>447861</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>436236</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>457725</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>599</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>413848</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>402271</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>422653</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>404176</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>423164</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>447861</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>436316</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>457725</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>846492</t>
+          <t>846902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>875390</t>
+          <t>874971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492755</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492755</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492755</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>451799</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>451799</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>451799</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492755</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492755</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492755</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10472</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23303</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9708</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15416</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5522</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16028</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10192</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22899</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18478</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155582</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148178</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161009</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>157104</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151396</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161530</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150784</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>161290</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>155582</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148582</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>161289</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303563</t>
+          <t>302832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319815</t>
+          <t>319591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171481</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171481</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171481</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171481</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171481</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>59838</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>86482</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40579</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>65077</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41292</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>63464</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>60991</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>86973</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108165</t>
+          <t>107258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143608</t>
+          <t>141274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>677051</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>663946</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>690590</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>659268</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>645903</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>670401</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>647516</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>669688</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>677051</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>663455</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>689437</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1317800</t>
+          <t>1320134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1353243</t>
+          <t>1354150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>750428</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>750428</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>750428</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>710980</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>710980</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>710980</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>750428</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>750428</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>750428</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5731</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5824</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5816</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66085</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62883</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67969</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56921</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53554</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>58767</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>53562</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58676</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66085</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62214</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67960</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118647</t>
+          <t>118548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125661</t>
+          <t>125565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23798</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41168</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10743</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23715</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11055</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24684</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31390</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23405</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40687</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59181</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>456683</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>446905</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>464275</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>688</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>455173</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>447958</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>460930</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>446989</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>460618</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>456683</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>447386</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>464668</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>900565</t>
+          <t>900160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>922411</t>
+          <t>922640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488073</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488073</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488073</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>471673</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>471673</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>471673</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488073</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488073</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488073</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11711</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8925</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8456</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12307</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>180011</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>175105</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>183529</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>166598</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162085</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>169190</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>162554</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>169192</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,42%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>180011</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>174509</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>183372</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>509</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>340543</t>
+          <t>340358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>350974</t>
+          <t>350941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186816</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186816</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186816</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>171010</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>171010</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>171010</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186816</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186816</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30622</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52365</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17224</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16176</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31456</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>31377</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52052</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>52656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76910</t>
+          <t>78791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>702779</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>691138</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>712881</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>678692</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>670285</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>684837</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>670605</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>685885</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>702779</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>691451</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>712126</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1368654</t>
+          <t>1366773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1392867</t>
+          <t>1392908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>702061</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>702061</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>702061</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5711</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4411</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6094</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55591</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51021</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53596</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50434</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42347</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60654</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55910</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>149</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114250</t>
+          <t>101224</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108929</t>
+          <t>96814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116048</t>
+          <t>103103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8316</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20652</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6204</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17037</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36541</t>
+          <t>34546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>460950</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>454027</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>466363</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>448259</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>442241</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>453074</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500793</t>
+          <t>420251</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492991</t>
+          <t>413823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505999</t>
+          <t>424949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>949053</t>
+          <t>881203</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>938277</t>
+          <t>871377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956672</t>
+          <t>888706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>474679</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>474679</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>474679</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459278</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459278</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459278</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515539</t>
+          <t>431243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515539</t>
+          <t>431243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515539</t>
+          <t>431243</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>974818</t>
+          <t>905923</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>974818</t>
+          <t>905923</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>974818</t>
+          <t>905923</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14606</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10100</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2265</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10368</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7937</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15791</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161037</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153813</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164717</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>144500</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>139451</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147247</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>144908</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>139608</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>147711</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>175412</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167558</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>179444</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>319912</t>
+          <t>305946</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312027</t>
+          <t>298240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325354</t>
+          <t>311261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14992</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32709</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10971</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24898</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>51370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>677579</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>667121</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>684838</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>646356</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>638609</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>652536</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>736858</t>
+          <t>610793</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>725834</t>
+          <t>601954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744524</t>
+          <t>616418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1383214</t>
+          <t>1288373</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1371528</t>
+          <t>1276438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1393698</t>
+          <t>1298441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663507</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663507</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663507</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424399</t>
+          <t>1327808</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424399</t>
+          <t>1327808</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424399</t>
+          <t>1327808</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
